--- a/cet4/result/04_修仙重生_女帝归来之路/04_修仙重生_女帝归来之路_学习版.xlsx
+++ b/cet4/result/04_修仙重生_女帝归来之路/04_修仙重生_女帝归来之路_学习版.xlsx
@@ -397,1137 +397,759 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D53"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>firm</v>
       </c>
       <c r="B2" t="str">
-        <v>firm</v>
+        <v>/fɜːrm/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D2" t="str">
         <v>坚固的</v>
       </c>
-      <c r="D2" t="str">
-        <v>firm(坚固的)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>universe</v>
       </c>
       <c r="B3" t="str">
-        <v>universe</v>
+        <v>/ˈjuːnɪvɜːrs/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>宇宙</v>
       </c>
-      <c r="D3" t="str">
-        <v>universe(宇宙)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>ampere</v>
       </c>
       <c r="B4" t="str">
-        <v>ampere</v>
+        <v>/æm'pɪr/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>安培</v>
       </c>
-      <c r="D4" t="str">
-        <v>ampere(安培)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>subject</v>
       </c>
       <c r="B5" t="str">
-        <v>subject</v>
+        <v>/ˈsʌbdʒɪkt/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./vt./adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>科目</v>
       </c>
-      <c r="D5" t="str">
-        <v>subject(科目)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>league</v>
       </c>
       <c r="B6" t="str">
-        <v>league</v>
+        <v>/liːɡ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>联盟</v>
       </c>
-      <c r="D6" t="str">
-        <v>league(联盟)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>employee</v>
       </c>
       <c r="B7" t="str">
-        <v>employee</v>
+        <v>/ɪmˈplɔɪiː/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>雇员</v>
       </c>
-      <c r="D7" t="str">
-        <v>employee(雇员)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>routine</v>
       </c>
       <c r="B8" t="str">
-        <v>routine</v>
+        <v>/ruːˈtiːn/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>常规</v>
       </c>
-      <c r="D8" t="str">
-        <v>routine(常规)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>want</v>
       </c>
       <c r="B9" t="str">
-        <v>want</v>
+        <v>/wɑːnt/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>想要</v>
       </c>
-      <c r="D9" t="str">
-        <v>want(想要)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>practice</v>
       </c>
       <c r="B10" t="str">
-        <v>practice</v>
+        <v>/ˈpræktɪs/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>练习</v>
       </c>
-      <c r="D10" t="str">
-        <v>practice(练习)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>rate</v>
       </c>
       <c r="B11" t="str">
-        <v>rate</v>
+        <v>/reɪt/</v>
       </c>
       <c r="C11" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>比率</v>
       </c>
-      <c r="D11" t="str">
-        <v>rate(比率)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>cage</v>
       </c>
       <c r="B12" t="str">
-        <v>cage</v>
+        <v>/keɪdʒ/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D12" t="str">
         <v>笼子</v>
       </c>
-      <c r="D12" t="str">
-        <v>cage(笼子)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>sweat</v>
       </c>
       <c r="B13" t="str">
-        <v>sweat</v>
+        <v>/swet/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D13" t="str">
         <v>汗水</v>
       </c>
-      <c r="D13" t="str">
-        <v>sweat(汗水)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>her</v>
       </c>
       <c r="B14" t="str">
-        <v>her</v>
+        <v>/hə(r)/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D14" t="str">
         <v>她的</v>
       </c>
-      <c r="D14" t="str">
-        <v>her(她的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>ninety</v>
       </c>
       <c r="B15" t="str">
-        <v>ninety</v>
+        <v>/ˈnaɪnti/</v>
       </c>
       <c r="C15" t="str">
+        <v>n./adj./num.</v>
+      </c>
+      <c r="D15" t="str">
         <v>九十</v>
       </c>
-      <c r="D15" t="str">
-        <v>ninety(九十)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>scholarship</v>
       </c>
       <c r="B16" t="str">
-        <v>scholarship</v>
+        <v>/ˈskɑːlərʃɪp/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>奖学金</v>
       </c>
-      <c r="D16" t="str">
-        <v>scholarship(奖学金)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>tourist</v>
       </c>
       <c r="B17" t="str">
-        <v>tourist</v>
+        <v>/ˈtʊrɪst/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>游客</v>
       </c>
-      <c r="D17" t="str">
-        <v>tourist(游客)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>overcoat</v>
       </c>
       <c r="B18" t="str">
-        <v>overcoat</v>
+        <v>/ˈoʊvərkoʊt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>大衣</v>
       </c>
-      <c r="D18" t="str">
-        <v>overcoat(大衣)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>introduce</v>
       </c>
       <c r="B19" t="str">
-        <v>tourist</v>
+        <v>/ˌɪntrəˈduːs/</v>
       </c>
       <c r="C19" t="str">
-        <v>游客</v>
+        <v>vt.</v>
       </c>
       <c r="D19" t="str">
-        <v>tourist(游客)📢</v>
+        <v>介绍</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>frown</v>
       </c>
       <c r="B20" t="str">
-        <v>introduce</v>
+        <v>/fraʊn/</v>
       </c>
       <c r="C20" t="str">
-        <v>介绍</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D20" t="str">
-        <v>introduce(介绍)📢</v>
+        <v>皱眉</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>great</v>
       </c>
       <c r="B21" t="str">
-        <v>frown</v>
+        <v>/ɡreɪt/</v>
       </c>
       <c r="C21" t="str">
-        <v>皱眉</v>
+        <v>n./adj.</v>
       </c>
       <c r="D21" t="str">
-        <v>frown(皱眉)📢</v>
+        <v>伟大的</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>cathedral</v>
       </c>
       <c r="B22" t="str">
-        <v>great</v>
+        <v>/kəˈθiːdrəl/</v>
       </c>
       <c r="C22" t="str">
-        <v>伟大的</v>
+        <v>n.</v>
       </c>
       <c r="D22" t="str">
-        <v>great(伟大的)📢</v>
+        <v>大教堂</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>infinite</v>
       </c>
       <c r="B23" t="str">
-        <v>cathedral</v>
+        <v>/ˈɪnfɪnət/</v>
       </c>
       <c r="C23" t="str">
-        <v>大教堂</v>
+        <v>n./adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>cathedral(大教堂)📢</v>
+        <v>无限的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>intermediate</v>
       </c>
       <c r="B24" t="str">
-        <v>infinite</v>
+        <v>/ˌɪntərˈmiːdiət/</v>
       </c>
       <c r="C24" t="str">
-        <v>无限的</v>
+        <v>n./v./adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>infinite(无限的)📢</v>
+        <v>中级的</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>lieutenant</v>
       </c>
       <c r="B25" t="str">
-        <v>intermediate</v>
+        <v>/luːˈtenənt/</v>
       </c>
       <c r="C25" t="str">
-        <v>中级的</v>
+        <v>n.</v>
       </c>
       <c r="D25" t="str">
-        <v>intermediate(中级的)📢</v>
+        <v>副官</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>refuse</v>
       </c>
       <c r="B26" t="str">
-        <v>lieutenant</v>
+        <v>/rɪˈfjuːz; ˈrefjuːs/</v>
       </c>
       <c r="C26" t="str">
-        <v>副官</v>
+        <v>n./vt.</v>
       </c>
       <c r="D26" t="str">
-        <v>lieutenant(副官)📢</v>
+        <v>拒绝</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>revise</v>
       </c>
       <c r="B27" t="str">
-        <v>refuse</v>
+        <v>/rɪˈvaɪz/</v>
       </c>
       <c r="C27" t="str">
-        <v>拒绝</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D27" t="str">
-        <v>refuse(拒绝)📢</v>
+        <v>修改</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>safe</v>
       </c>
       <c r="B28" t="str">
-        <v>revise</v>
+        <v>/seɪf/</v>
       </c>
       <c r="C28" t="str">
-        <v>修改</v>
+        <v>n./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>revise(修改)📢</v>
+        <v>安全</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>join</v>
       </c>
       <c r="B29" t="str">
-        <v>safe</v>
+        <v>/dʒɔɪn/</v>
       </c>
       <c r="C29" t="str">
-        <v>安全</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>safe(安全)📢</v>
+        <v>加入</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>snake</v>
       </c>
       <c r="B30" t="str">
-        <v>join</v>
+        <v>/sneɪk/</v>
       </c>
       <c r="C30" t="str">
-        <v>加入</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D30" t="str">
-        <v>join(加入)📢</v>
+        <v>蛇</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>hardship</v>
       </c>
       <c r="B31" t="str">
-        <v>snake</v>
+        <v>/ˈhɑːrdʃɪp/</v>
       </c>
       <c r="C31" t="str">
-        <v>蛇</v>
+        <v>n.</v>
       </c>
       <c r="D31" t="str">
-        <v>snake(蛇)📢</v>
+        <v>困苦</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>namely</v>
       </c>
       <c r="B32" t="str">
-        <v>hardship</v>
+        <v>/ˈneɪmli/</v>
       </c>
       <c r="C32" t="str">
-        <v>困苦</v>
+        <v>v./adv.</v>
       </c>
       <c r="D32" t="str">
-        <v>hardship(困苦)📢</v>
+        <v>即</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>air</v>
       </c>
       <c r="B33" t="str">
-        <v>namely</v>
+        <v>/er/</v>
       </c>
       <c r="C33" t="str">
-        <v>即</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>namely(即)📢</v>
+        <v>空气</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>touch</v>
       </c>
       <c r="B34" t="str">
-        <v>snake</v>
+        <v>/tʌtʃ/</v>
       </c>
       <c r="C34" t="str">
-        <v>蛇</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>snake(蛇)📢</v>
+        <v>触摸</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>crisis</v>
       </c>
       <c r="B35" t="str">
-        <v>air</v>
+        <v>/ˈkraɪsɪs/</v>
       </c>
       <c r="C35" t="str">
-        <v>空气</v>
+        <v>n./adj.</v>
       </c>
       <c r="D35" t="str">
-        <v>air(空气)📢</v>
+        <v>危机</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>suspicion</v>
       </c>
       <c r="B36" t="str">
-        <v>touch</v>
+        <v>/səˈspɪʃn/</v>
       </c>
       <c r="C36" t="str">
-        <v>触摸</v>
+        <v>n./vt.</v>
       </c>
       <c r="D36" t="str">
-        <v>touch(触摸)📢</v>
+        <v>怀疑</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>vex</v>
       </c>
       <c r="B37" t="str">
-        <v>snake</v>
+        <v>/veks/</v>
       </c>
       <c r="C37" t="str">
-        <v>蛇</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>snake(蛇)📢</v>
+        <v>烦恼</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>holiday</v>
       </c>
       <c r="B38" t="str">
-        <v>revise</v>
+        <v>/ˈhɑːlədeɪ/</v>
       </c>
       <c r="C38" t="str">
-        <v>修改</v>
+        <v>n./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>revise(修改)📢</v>
+        <v>节日</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>nitrogen</v>
       </c>
       <c r="B39" t="str">
-        <v>crisis</v>
+        <v>/ˈnaɪtrədʒən/</v>
       </c>
       <c r="C39" t="str">
-        <v>危机</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>crisis(危机)📢</v>
+        <v>氮</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>margin</v>
       </c>
       <c r="B40" t="str">
-        <v>employee</v>
+        <v>/ˈmɑːrdʒɪn/</v>
       </c>
       <c r="C40" t="str">
-        <v>雇员</v>
+        <v>n./vt.</v>
       </c>
       <c r="D40" t="str">
-        <v>employee(雇员)📢</v>
+        <v>余地</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>phase</v>
       </c>
       <c r="B41" t="str">
-        <v>want</v>
+        <v>/feɪz/</v>
       </c>
       <c r="C41" t="str">
-        <v>想要</v>
+        <v>n./vt.</v>
       </c>
       <c r="D41" t="str">
-        <v>want(想要)📢</v>
+        <v>阶段</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>rush</v>
       </c>
       <c r="B42" t="str">
-        <v>namely</v>
+        <v>/rʌʃ/</v>
       </c>
       <c r="C42" t="str">
-        <v>即</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>namely(即)📢</v>
+        <v>急促</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>motivate</v>
       </c>
       <c r="B43" t="str">
-        <v>intermediate</v>
+        <v>/ˈmoʊtɪveɪt/</v>
       </c>
       <c r="C43" t="str">
-        <v>中间</v>
+        <v>v.</v>
       </c>
       <c r="D43" t="str">
-        <v>intermediate(中间)📢</v>
+        <v>激励</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>expense</v>
       </c>
       <c r="B44" t="str">
-        <v>suspicion</v>
+        <v>/ɪkˈspens/</v>
       </c>
       <c r="C44" t="str">
-        <v>怀疑</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D44" t="str">
-        <v>suspicion(怀疑)📢</v>
+        <v>代价</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>pigeon</v>
       </c>
       <c r="B45" t="str">
-        <v>vex</v>
+        <v>/ˈpɪdʒɪn/</v>
       </c>
       <c r="C45" t="str">
-        <v>烦恼</v>
+        <v>n.</v>
       </c>
       <c r="D45" t="str">
-        <v>vex(烦恼)📢</v>
+        <v>鸽子</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>brim</v>
       </c>
       <c r="B46" t="str">
-        <v>holiday</v>
+        <v>/brɪm/</v>
       </c>
       <c r="C46" t="str">
-        <v>节日</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D46" t="str">
-        <v>holiday(节日)📢</v>
+        <v>边缘</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>happy</v>
       </c>
       <c r="B47" t="str">
-        <v>great</v>
+        <v>/ˈhæpi/</v>
       </c>
       <c r="C47" t="str">
-        <v>盛大的</v>
+        <v>n./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>great(盛大的)📢</v>
+        <v>快乐</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>porter</v>
       </c>
       <c r="B48" t="str">
-        <v>lieutenant</v>
+        <v>/'potər/</v>
       </c>
       <c r="C48" t="str">
-        <v>副掌门</v>
+        <v>n.</v>
       </c>
       <c r="D48" t="str">
-        <v>lieutenant(副掌门)📢</v>
+        <v>搬运工</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>due</v>
       </c>
       <c r="B49" t="str">
-        <v>want</v>
+        <v>/duː/</v>
       </c>
       <c r="C49" t="str">
-        <v>想要</v>
+        <v>n./v./adj./adv.</v>
       </c>
       <c r="D49" t="str">
-        <v>want(想要)📢</v>
+        <v>到期</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>bake</v>
       </c>
       <c r="B50" t="str">
-        <v>nitrogen</v>
+        <v>/beɪk/</v>
       </c>
       <c r="C50" t="str">
-        <v>氮</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>nitrogen(氮)📢</v>
+        <v>烘烤</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>tie</v>
       </c>
       <c r="B51" t="str">
-        <v>join</v>
+        <v>/taɪ/</v>
       </c>
       <c r="C51" t="str">
-        <v>加入</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D51" t="str">
-        <v>join(加入)📢</v>
+        <v>领带</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52">
-        <v>51</v>
+      <c r="A52" t="str">
+        <v>inspire</v>
       </c>
       <c r="B52" t="str">
-        <v>margin</v>
+        <v>/ɪnˈspaɪər/</v>
       </c>
       <c r="C52" t="str">
-        <v>余地</v>
+        <v>vt.</v>
       </c>
       <c r="D52" t="str">
-        <v>margin(余地)📢</v>
+        <v>激发</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53">
-        <v>52</v>
+      <c r="A53" t="str">
+        <v>rotation</v>
       </c>
       <c r="B53" t="str">
-        <v>phase</v>
+        <v>/roʊˈteɪʃn/</v>
       </c>
       <c r="C53" t="str">
-        <v>阶段</v>
+        <v>n.</v>
       </c>
       <c r="D53" t="str">
-        <v>phase(阶段)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>crisis</v>
-      </c>
-      <c r="C54" t="str">
-        <v>危机</v>
-      </c>
-      <c r="D54" t="str">
-        <v>crisis(危机)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>refuse</v>
-      </c>
-      <c r="C55" t="str">
-        <v>拒绝</v>
-      </c>
-      <c r="D55" t="str">
-        <v>refuse(拒绝)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>rush</v>
-      </c>
-      <c r="C56" t="str">
-        <v>急促</v>
-      </c>
-      <c r="D56" t="str">
-        <v>rush(急促)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>motivate</v>
-      </c>
-      <c r="C57" t="str">
-        <v>激励</v>
-      </c>
-      <c r="D57" t="str">
-        <v>motivate(激励)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>expense</v>
-      </c>
-      <c r="C58" t="str">
-        <v>代价</v>
-      </c>
-      <c r="D58" t="str">
-        <v>expense(代价)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>hardship</v>
-      </c>
-      <c r="C59" t="str">
-        <v>艰难</v>
-      </c>
-      <c r="D59" t="str">
-        <v>hardship(艰难)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>pigeon</v>
-      </c>
-      <c r="C60" t="str">
-        <v>鸽子</v>
-      </c>
-      <c r="D60" t="str">
-        <v>pigeon(鸽子)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>air</v>
-      </c>
-      <c r="C61" t="str">
-        <v>空气</v>
-      </c>
-      <c r="D61" t="str">
-        <v>air(空气)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>infinite</v>
-      </c>
-      <c r="C62" t="str">
-        <v>无限</v>
-      </c>
-      <c r="D62" t="str">
-        <v>infinite(无限)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>overcoat</v>
-      </c>
-      <c r="C63" t="str">
-        <v>大衣</v>
-      </c>
-      <c r="D63" t="str">
-        <v>overcoat(大衣)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>brim</v>
-      </c>
-      <c r="C64" t="str">
-        <v>边缘</v>
-      </c>
-      <c r="D64" t="str">
-        <v>brim(边缘)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>practice</v>
-      </c>
-      <c r="C65" t="str">
-        <v>练习</v>
-      </c>
-      <c r="D65" t="str">
-        <v>practice(练习)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>happy</v>
-      </c>
-      <c r="C66" t="str">
-        <v>快乐</v>
-      </c>
-      <c r="D66" t="str">
-        <v>happy(快乐)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>porter</v>
-      </c>
-      <c r="C67" t="str">
-        <v>搬运工</v>
-      </c>
-      <c r="D67" t="str">
-        <v>porter(搬运工)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>due</v>
-      </c>
-      <c r="C68" t="str">
-        <v>到期</v>
-      </c>
-      <c r="D68" t="str">
-        <v>due(到期)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>snake</v>
-      </c>
-      <c r="C69" t="str">
-        <v>蛇</v>
-      </c>
-      <c r="D69" t="str">
-        <v>snake(蛇)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>bake</v>
-      </c>
-      <c r="C70" t="str">
-        <v>烘烤</v>
-      </c>
-      <c r="D70" t="str">
-        <v>bake(烘烤)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>want</v>
-      </c>
-      <c r="C71" t="str">
-        <v>想要</v>
-      </c>
-      <c r="D71" t="str">
-        <v>want(想要)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>refuse</v>
-      </c>
-      <c r="C72" t="str">
-        <v>拒绝</v>
-      </c>
-      <c r="D72" t="str">
-        <v>refuse(拒绝)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>league</v>
-      </c>
-      <c r="C73" t="str">
-        <v>联盟</v>
-      </c>
-      <c r="D73" t="str">
-        <v>league(联盟)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>tie</v>
-      </c>
-      <c r="C74" t="str">
-        <v>领带</v>
-      </c>
-      <c r="D74" t="str">
-        <v>tie(领带)📢</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>tourist</v>
-      </c>
-      <c r="C75" t="str">
-        <v>游客</v>
-      </c>
-      <c r="D75" t="str">
-        <v>tourist(游客)📢</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76">
-        <v>75</v>
-      </c>
-      <c r="B76" t="str">
-        <v>inspire</v>
-      </c>
-      <c r="C76" t="str">
-        <v>激发</v>
-      </c>
-      <c r="D76" t="str">
-        <v>inspire(激发)📢</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77">
-        <v>76</v>
-      </c>
-      <c r="B77" t="str">
-        <v>cathedral</v>
-      </c>
-      <c r="C77" t="str">
-        <v>教堂</v>
-      </c>
-      <c r="D77" t="str">
-        <v>cathedral(教堂)📢</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78">
-        <v>77</v>
-      </c>
-      <c r="B78" t="str">
-        <v>suspicion</v>
-      </c>
-      <c r="C78" t="str">
-        <v>怀疑</v>
-      </c>
-      <c r="D78" t="str">
-        <v>suspicion(怀疑)📢</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79">
-        <v>78</v>
-      </c>
-      <c r="B79" t="str">
-        <v>infinite</v>
-      </c>
-      <c r="C79" t="str">
-        <v>无限</v>
-      </c>
-      <c r="D79" t="str">
-        <v>infinite(无限)📢</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80">
-        <v>79</v>
-      </c>
-      <c r="B80" t="str">
-        <v>rotation</v>
-      </c>
-      <c r="C80" t="str">
         <v>循环</v>
-      </c>
-      <c r="D80" t="str">
-        <v>rotation(循环)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D80"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D53"/>
   </ignoredErrors>
 </worksheet>
 </file>